--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260831.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260831.xlsx
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>107,708,350</t>
+          <t>25,406,762</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>25,406,762</t>
+          <t>107,708,350</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
